--- a/实验记录.xlsx
+++ b/实验记录.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ResearchCode\Idea\HtFLlib-1.8.1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wuxinghao/Documents/联邦学习/ResearchCode/FedTSP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0640F0EC-7CD9-47D7-9905-5964368903C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF4DE11B-160B-FD4A-A33E-B7BD4B2869EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21390" yWindow="4815" windowWidth="20475" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28620" yWindow="-8380" windowWidth="28600" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="30">
   <si>
     <t>验证文本prompt对训练的影响</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -149,6 +149,10 @@
   </si>
   <si>
     <t>alter 4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18.58 on 3090, p_prompt=1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -156,7 +160,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,15 +478,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q60"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:S60"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="B2" t="s">
         <v>2</v>
       </c>
@@ -502,7 +506,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -513,7 +517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -527,7 +531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>1</v>
       </c>
@@ -544,7 +548,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>1</v>
       </c>
@@ -561,7 +565,7 @@
         <v>84.57</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>0</v>
       </c>
@@ -581,7 +585,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8">
       <c r="B10" t="s">
         <v>2</v>
       </c>
@@ -601,7 +605,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -609,7 +613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>1</v>
       </c>
@@ -623,7 +627,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>1</v>
       </c>
@@ -637,7 +641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>1</v>
       </c>
@@ -657,7 +661,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>0</v>
       </c>
@@ -677,7 +681,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>2</v>
       </c>
@@ -694,7 +698,7 @@
         <v>53.74</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>3</v>
       </c>
@@ -714,7 +718,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>2</v>
       </c>
@@ -725,7 +729,7 @@
         <v>55.36</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>3</v>
       </c>
@@ -736,7 +740,7 @@
         <v>55.58</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>4</v>
       </c>
@@ -747,7 +751,7 @@
         <v>56.52</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>4</v>
       </c>
@@ -758,7 +762,7 @@
         <v>55.68</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>4</v>
       </c>
@@ -772,7 +776,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>10</v>
       </c>
@@ -783,7 +787,7 @@
         <v>56.19</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>5</v>
       </c>
@@ -794,7 +798,7 @@
         <v>55.72</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>5</v>
       </c>
@@ -805,7 +809,7 @@
         <v>56.91</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>5</v>
       </c>
@@ -819,7 +823,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>6</v>
       </c>
@@ -830,7 +834,7 @@
         <v>56.93</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>6</v>
       </c>
@@ -844,7 +848,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>7</v>
       </c>
@@ -855,7 +859,7 @@
         <v>56.64</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>7</v>
       </c>
@@ -869,7 +873,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>8</v>
       </c>
@@ -880,7 +884,7 @@
         <v>56.66</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8">
       <c r="A32">
         <v>8</v>
       </c>
@@ -894,7 +898,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:19">
       <c r="A33">
         <v>7</v>
       </c>
@@ -908,7 +912,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>7</v>
       </c>
@@ -919,7 +923,7 @@
         <v>56.66</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>7</v>
       </c>
@@ -933,7 +937,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:19">
       <c r="B37" t="s">
         <v>19</v>
       </c>
@@ -947,7 +951,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:19">
       <c r="A38" t="s">
         <v>20</v>
       </c>
@@ -958,15 +962,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:19">
       <c r="J39" t="s">
         <v>25</v>
       </c>
-      <c r="N39" t="s">
+      <c r="P39" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:19">
       <c r="A40" t="s">
         <v>1</v>
       </c>
@@ -991,20 +995,20 @@
       <c r="L40" t="s">
         <v>23</v>
       </c>
-      <c r="N40" t="s">
-        <v>1</v>
-      </c>
-      <c r="O40" t="s">
-        <v>6</v>
-      </c>
       <c r="P40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>6</v>
+      </c>
+      <c r="R40" t="s">
         <v>27</v>
       </c>
-      <c r="Q40" t="s">
+      <c r="S40" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:19">
       <c r="J41">
         <v>0</v>
       </c>
@@ -1014,14 +1018,14 @@
       <c r="L41">
         <v>300</v>
       </c>
-      <c r="N41">
-        <v>1</v>
-      </c>
-      <c r="O41">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="P41">
+        <v>1</v>
+      </c>
+      <c r="Q41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19">
       <c r="J42">
         <v>1</v>
       </c>
@@ -1031,20 +1035,20 @@
       <c r="L42">
         <v>300</v>
       </c>
-      <c r="N42">
+      <c r="P42">
         <v>2</v>
       </c>
-      <c r="O42">
-        <v>5</v>
-      </c>
-      <c r="P42">
+      <c r="Q42">
+        <v>5</v>
+      </c>
+      <c r="R42">
         <v>17.38</v>
       </c>
-      <c r="Q42">
+      <c r="S42">
         <v>219</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:19">
       <c r="J43">
         <v>2</v>
       </c>
@@ -1054,17 +1058,17 @@
       <c r="L43">
         <v>300</v>
       </c>
-      <c r="N43">
+      <c r="P43">
         <v>3</v>
       </c>
-      <c r="O43">
-        <v>5</v>
-      </c>
-      <c r="P43">
+      <c r="Q43">
+        <v>5</v>
+      </c>
+      <c r="R43">
         <v>17.82</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:19">
       <c r="J44">
         <v>3</v>
       </c>
@@ -1074,17 +1078,17 @@
       <c r="L44">
         <v>300</v>
       </c>
-      <c r="N44">
+      <c r="P44">
         <v>4</v>
       </c>
-      <c r="O44">
-        <v>5</v>
-      </c>
-      <c r="P44">
+      <c r="Q44">
+        <v>5</v>
+      </c>
+      <c r="R44">
         <v>18.04</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:19">
       <c r="J45">
         <v>4</v>
       </c>
@@ -1094,17 +1098,17 @@
       <c r="L45">
         <v>300</v>
       </c>
-      <c r="N45">
-        <v>5</v>
-      </c>
-      <c r="O45">
-        <v>5</v>
-      </c>
       <c r="P45">
+        <v>5</v>
+      </c>
+      <c r="Q45">
+        <v>5</v>
+      </c>
+      <c r="R45">
         <v>18.09</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:19">
       <c r="J46">
         <v>5</v>
       </c>
@@ -1114,17 +1118,17 @@
       <c r="L46">
         <v>300</v>
       </c>
-      <c r="N46">
-        <v>6</v>
-      </c>
-      <c r="O46">
-        <v>5</v>
-      </c>
       <c r="P46">
+        <v>6</v>
+      </c>
+      <c r="Q46">
+        <v>5</v>
+      </c>
+      <c r="R46">
         <v>18.14</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:19">
       <c r="J47">
         <v>6</v>
       </c>
@@ -1134,17 +1138,20 @@
       <c r="L47">
         <v>300</v>
       </c>
-      <c r="N47">
+      <c r="M47" t="s">
+        <v>29</v>
+      </c>
+      <c r="P47">
         <v>7</v>
       </c>
-      <c r="O47">
-        <v>5</v>
-      </c>
-      <c r="P47">
+      <c r="Q47">
+        <v>5</v>
+      </c>
+      <c r="R47">
         <v>18.55</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:19">
       <c r="J48">
         <v>7</v>
       </c>
@@ -1154,17 +1161,17 @@
       <c r="L48">
         <v>100</v>
       </c>
-      <c r="N48">
+      <c r="P48">
         <v>8</v>
       </c>
-      <c r="O48">
-        <v>5</v>
-      </c>
-      <c r="P48">
+      <c r="Q48">
+        <v>5</v>
+      </c>
+      <c r="R48">
         <v>18.260000000000002</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>6</v>
       </c>
@@ -1190,7 +1197,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>6</v>
       </c>
@@ -1207,7 +1214,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>6</v>
       </c>
@@ -1229,11 +1236,11 @@
       <c r="J51" t="s">
         <v>17</v>
       </c>
-      <c r="N51" t="s">
+      <c r="P51" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:19">
       <c r="J52" t="s">
         <v>1</v>
       </c>
@@ -1243,76 +1250,76 @@
       <c r="L52" t="s">
         <v>27</v>
       </c>
-      <c r="N52" t="s">
-        <v>1</v>
-      </c>
-      <c r="O52" t="s">
-        <v>6</v>
-      </c>
       <c r="P52" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>6</v>
+      </c>
+      <c r="R52" t="s">
         <v>27</v>
       </c>
-      <c r="Q52" t="s">
+      <c r="S52" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:19">
       <c r="J53">
         <v>1</v>
       </c>
       <c r="K53">
         <v>5</v>
       </c>
-      <c r="N53">
-        <v>1</v>
-      </c>
-      <c r="O53">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="P53">
+        <v>1</v>
+      </c>
+      <c r="Q53">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19">
       <c r="J54">
         <v>2</v>
       </c>
       <c r="K54">
         <v>5</v>
       </c>
-      <c r="N54">
+      <c r="P54">
         <v>2</v>
       </c>
-      <c r="O54">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q54">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19">
       <c r="J55">
         <v>3</v>
       </c>
       <c r="K55">
         <v>5</v>
       </c>
-      <c r="N55">
+      <c r="P55">
         <v>3</v>
       </c>
-      <c r="O55">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q55">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19">
       <c r="J56">
         <v>4</v>
       </c>
       <c r="K56">
         <v>5</v>
       </c>
-      <c r="N56">
+      <c r="P56">
         <v>4</v>
       </c>
-      <c r="O56">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19">
       <c r="J57">
         <v>5</v>
       </c>
@@ -1322,17 +1329,17 @@
       <c r="L57">
         <v>18.45</v>
       </c>
-      <c r="N57">
-        <v>5</v>
-      </c>
-      <c r="O57">
-        <v>5</v>
-      </c>
       <c r="P57">
+        <v>5</v>
+      </c>
+      <c r="Q57">
+        <v>5</v>
+      </c>
+      <c r="R57">
         <v>18.34</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:19">
       <c r="J58">
         <v>6</v>
       </c>
@@ -1342,44 +1349,44 @@
       <c r="L58">
         <v>18.91</v>
       </c>
-      <c r="N58">
-        <v>6</v>
-      </c>
-      <c r="O58">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="P58">
+        <v>6</v>
+      </c>
+      <c r="Q58">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19">
       <c r="J59">
         <v>7</v>
       </c>
       <c r="K59">
         <v>5</v>
       </c>
-      <c r="N59">
+      <c r="P59">
         <v>7</v>
       </c>
-      <c r="O59">
-        <v>5</v>
-      </c>
-      <c r="P59">
+      <c r="Q59">
+        <v>5</v>
+      </c>
+      <c r="R59">
         <v>19.010000000000002</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:19">
       <c r="J60">
         <v>8</v>
       </c>
       <c r="K60">
         <v>5</v>
       </c>
-      <c r="N60">
+      <c r="P60">
         <v>8</v>
       </c>
-      <c r="O60">
-        <v>5</v>
-      </c>
-      <c r="P60">
+      <c r="Q60">
+        <v>5</v>
+      </c>
+      <c r="R60">
         <v>18.63</v>
       </c>
     </row>

--- a/实验记录.xlsx
+++ b/实验记录.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wuxinghao/Documents/联邦学习/ResearchCode/FedTSP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF4DE11B-160B-FD4A-A33E-B7BD4B2869EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D776B910-A0FA-5841-87A6-5DA13CB2A55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28620" yWindow="-8380" windowWidth="28600" windowHeight="15880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="CIFAR100-dir1.0-client20" sheetId="3" r:id="rId1"/>
+    <sheet name="CIFAR10-dir1.0-client20" sheetId="4" r:id="rId2"/>
+    <sheet name="v2" sheetId="2" r:id="rId3"/>
+    <sheet name="v1" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="60">
   <si>
     <t>验证文本prompt对训练的影响</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -155,6 +159,126 @@
     <t>18.58 on 3090, p_prompt=1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>plr=0.001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CSC=false</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>local_ep=1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在v1中加入个性化prompt的代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新添加v2，将textencoder放置在服务器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>p_prompt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vision</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vision_lamda</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prompt_epoch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>best round</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>train acc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>note</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>31轮时ResNet CE：0.00x, CLIP:0.000x。CNN CE: 0.x, CLIP: 0.0x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6x轮时开始train动。94轮时ResNet CE: 0.1x CLIP: 1.x.  CNN CE:0.2-1.x, CLIP: 3.x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在38轮时，CLIP loss都降到0.x和0.0x水平，但是CNN的CE还比较高1.x-3.x</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>与上个实验类似，但是CNN的CE似乎小了一些</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CSC=False, plr=0.001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CSC=False</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EMA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作为2的对应实验，设置EMA后模型可以正常对齐文本特征</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>相当于随机初始化prompt不训练，plr=0.0001。但相当于不起作用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plr=0.0001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>random_init</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HtFE2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>base</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>try</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12-66实验：60轮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -176,12 +300,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -196,8 +338,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -477,8 +622,5303 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CCDCA62-1458-6748-AAD6-300D2625CB6F}">
+  <dimension ref="A1:Q118"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:17">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>18.07</v>
+      </c>
+      <c r="G3">
+        <v>15</v>
+      </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>22.51</v>
+      </c>
+      <c r="G4">
+        <v>32</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M4">
+        <v>0.1</v>
+      </c>
+      <c r="N4">
+        <v>15.99</v>
+      </c>
+      <c r="P4">
+        <v>0.1</v>
+      </c>
+      <c r="Q4">
+        <v>20.25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>21.78</v>
+      </c>
+      <c r="G5">
+        <v>26</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
+        <v>50</v>
+      </c>
+      <c r="M5">
+        <v>0.2</v>
+      </c>
+      <c r="P5">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>22.66</v>
+      </c>
+      <c r="G6">
+        <v>24</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6">
+        <v>0.3</v>
+      </c>
+      <c r="P6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>22.83</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7">
+        <v>0.4</v>
+      </c>
+      <c r="P7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1">
+        <v>7</v>
+      </c>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>23.14</v>
+      </c>
+      <c r="G8" s="1">
+        <v>20</v>
+      </c>
+      <c r="H8" s="1">
+        <v>100</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8">
+        <v>0.5</v>
+      </c>
+      <c r="P8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>23.12</v>
+      </c>
+      <c r="G9">
+        <v>20</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>8</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>9</v>
+      </c>
+      <c r="F10">
+        <v>22.46</v>
+      </c>
+      <c r="G10">
+        <v>14</v>
+      </c>
+      <c r="H10">
+        <v>100</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>23.24</v>
+      </c>
+      <c r="G11">
+        <v>18</v>
+      </c>
+      <c r="H11">
+        <v>100</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>7</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>23.16</v>
+      </c>
+      <c r="G16">
+        <v>18</v>
+      </c>
+      <c r="H16">
+        <v>100</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>7</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>22.56</v>
+      </c>
+      <c r="G17">
+        <v>21</v>
+      </c>
+      <c r="H17">
+        <v>100</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>7</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>23.23</v>
+      </c>
+      <c r="G18">
+        <v>21</v>
+      </c>
+      <c r="H18">
+        <v>100</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19">
+        <v>4</v>
+      </c>
+      <c r="B19">
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>22.97</v>
+      </c>
+      <c r="G19">
+        <v>20</v>
+      </c>
+      <c r="H19">
+        <v>100</v>
+      </c>
+      <c r="I19">
+        <v>0.99</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20">
+        <v>7</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>23.14</v>
+      </c>
+      <c r="G20">
+        <v>19</v>
+      </c>
+      <c r="H20">
+        <v>100</v>
+      </c>
+      <c r="I20">
+        <v>0.999</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21">
+        <v>6</v>
+      </c>
+      <c r="B21">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>23.06</v>
+      </c>
+      <c r="G21">
+        <v>22</v>
+      </c>
+      <c r="H21">
+        <v>100</v>
+      </c>
+      <c r="I21">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22">
+        <v>7</v>
+      </c>
+      <c r="B22">
+        <v>7</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>22.1</v>
+      </c>
+      <c r="G22">
+        <v>23</v>
+      </c>
+      <c r="H22">
+        <v>100</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23">
+        <v>8</v>
+      </c>
+      <c r="B23">
+        <v>7</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <v>23.06</v>
+      </c>
+      <c r="G23">
+        <v>23</v>
+      </c>
+      <c r="H23">
+        <v>100</v>
+      </c>
+      <c r="I23">
+        <v>0.9</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24">
+        <v>9</v>
+      </c>
+      <c r="B24">
+        <v>7</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
+      </c>
+      <c r="F24">
+        <v>23.2</v>
+      </c>
+      <c r="G24">
+        <v>21</v>
+      </c>
+      <c r="H24">
+        <v>100</v>
+      </c>
+      <c r="I24">
+        <v>0.99</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25">
+        <v>10</v>
+      </c>
+      <c r="B25">
+        <v>7</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>2</v>
+      </c>
+      <c r="F25" s="3">
+        <v>23.34</v>
+      </c>
+      <c r="G25">
+        <v>19</v>
+      </c>
+      <c r="H25">
+        <v>100</v>
+      </c>
+      <c r="I25">
+        <v>0.999</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>7</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <v>23.21</v>
+      </c>
+      <c r="G26">
+        <v>21</v>
+      </c>
+      <c r="H26">
+        <v>100</v>
+      </c>
+      <c r="I26">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27">
+        <v>12</v>
+      </c>
+      <c r="B27">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+      <c r="F27">
+        <v>20.87</v>
+      </c>
+      <c r="G27">
+        <v>47</v>
+      </c>
+      <c r="H27">
+        <v>99.3</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28">
+        <v>13</v>
+      </c>
+      <c r="B28">
+        <v>7</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>3</v>
+      </c>
+      <c r="F28">
+        <v>22.52</v>
+      </c>
+      <c r="G28">
+        <v>20</v>
+      </c>
+      <c r="H28">
+        <v>100</v>
+      </c>
+      <c r="I28">
+        <v>0.9</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29">
+        <v>14</v>
+      </c>
+      <c r="B29">
+        <v>7</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>3</v>
+      </c>
+      <c r="F29">
+        <v>22.85</v>
+      </c>
+      <c r="G29">
+        <v>22</v>
+      </c>
+      <c r="H29">
+        <v>100</v>
+      </c>
+      <c r="I29">
+        <v>0.99</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30">
+        <v>15</v>
+      </c>
+      <c r="B30">
+        <v>7</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
+      </c>
+      <c r="F30">
+        <v>22.67</v>
+      </c>
+      <c r="G30">
+        <v>21</v>
+      </c>
+      <c r="H30">
+        <v>100</v>
+      </c>
+      <c r="I30">
+        <v>0.999</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31">
+        <v>16</v>
+      </c>
+      <c r="B31">
+        <v>7</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>4</v>
+      </c>
+      <c r="F31">
+        <v>21.22</v>
+      </c>
+      <c r="G31">
+        <v>42</v>
+      </c>
+      <c r="H31">
+        <v>98.71</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32">
+        <v>17</v>
+      </c>
+      <c r="B32">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>4</v>
+      </c>
+      <c r="F32">
+        <v>22.41</v>
+      </c>
+      <c r="G32">
+        <v>21</v>
+      </c>
+      <c r="H32">
+        <v>99.81</v>
+      </c>
+      <c r="I32">
+        <v>0.9</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33">
+        <v>18</v>
+      </c>
+      <c r="B33">
+        <v>7</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>4</v>
+      </c>
+      <c r="F33">
+        <v>22.86</v>
+      </c>
+      <c r="G33">
+        <v>19</v>
+      </c>
+      <c r="H33">
+        <v>100</v>
+      </c>
+      <c r="I33">
+        <v>0.99</v>
+      </c>
+      <c r="J33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34">
+        <v>19</v>
+      </c>
+      <c r="B34">
+        <v>7</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>4</v>
+      </c>
+      <c r="F34">
+        <v>22.75</v>
+      </c>
+      <c r="G34">
+        <v>21</v>
+      </c>
+      <c r="H34">
+        <v>100</v>
+      </c>
+      <c r="I34">
+        <v>0.999</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35">
+        <v>20</v>
+      </c>
+      <c r="B35">
+        <v>7</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>5</v>
+      </c>
+      <c r="F35">
+        <v>21.09</v>
+      </c>
+      <c r="G35">
+        <v>48</v>
+      </c>
+      <c r="H35">
+        <v>98.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36">
+        <v>21</v>
+      </c>
+      <c r="B36">
+        <v>7</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>5</v>
+      </c>
+      <c r="F36">
+        <v>22.26</v>
+      </c>
+      <c r="G36">
+        <v>24</v>
+      </c>
+      <c r="H36">
+        <v>99.84</v>
+      </c>
+      <c r="I36">
+        <v>0.9</v>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37">
+        <v>22</v>
+      </c>
+      <c r="B37">
+        <v>7</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>5</v>
+      </c>
+      <c r="F37">
+        <v>22.87</v>
+      </c>
+      <c r="G37">
+        <v>22</v>
+      </c>
+      <c r="H37">
+        <v>100</v>
+      </c>
+      <c r="I37">
+        <v>0.99</v>
+      </c>
+      <c r="J37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38">
+        <v>23</v>
+      </c>
+      <c r="B38">
+        <v>7</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>5</v>
+      </c>
+      <c r="F38">
+        <v>22.96</v>
+      </c>
+      <c r="G38">
+        <v>20</v>
+      </c>
+      <c r="H38">
+        <v>100</v>
+      </c>
+      <c r="I38">
+        <v>0.999</v>
+      </c>
+      <c r="J38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39">
+        <v>24</v>
+      </c>
+      <c r="B39">
+        <v>7</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>3</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <v>20.87</v>
+      </c>
+      <c r="G39">
+        <v>33</v>
+      </c>
+      <c r="H39">
+        <v>99.42</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40">
+        <v>25</v>
+      </c>
+      <c r="B40">
+        <v>7</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <v>3</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <v>22.57</v>
+      </c>
+      <c r="G40">
+        <v>24</v>
+      </c>
+      <c r="H40">
+        <v>99.9</v>
+      </c>
+      <c r="I40">
+        <v>0.9</v>
+      </c>
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41">
+        <v>26</v>
+      </c>
+      <c r="B41">
+        <v>7</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>3</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>22.74</v>
+      </c>
+      <c r="G41">
+        <v>22</v>
+      </c>
+      <c r="H41">
+        <v>100</v>
+      </c>
+      <c r="I41">
+        <v>0.99</v>
+      </c>
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42">
+        <v>27</v>
+      </c>
+      <c r="B42">
+        <v>7</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>3</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>22.89</v>
+      </c>
+      <c r="G42">
+        <v>24</v>
+      </c>
+      <c r="H42">
+        <v>100</v>
+      </c>
+      <c r="I42">
+        <v>0.999</v>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43">
+        <v>28</v>
+      </c>
+      <c r="B43">
+        <v>7</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>3</v>
+      </c>
+      <c r="E43">
+        <v>2</v>
+      </c>
+      <c r="F43">
+        <v>21.43</v>
+      </c>
+      <c r="G43">
+        <v>49</v>
+      </c>
+      <c r="H43">
+        <v>98.02</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44">
+        <v>29</v>
+      </c>
+      <c r="B44">
+        <v>7</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>3</v>
+      </c>
+      <c r="E44">
+        <v>2</v>
+      </c>
+      <c r="F44">
+        <v>21.5</v>
+      </c>
+      <c r="G44">
+        <v>29</v>
+      </c>
+      <c r="H44">
+        <v>99.51</v>
+      </c>
+      <c r="I44">
+        <v>0.9</v>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45">
+        <v>30</v>
+      </c>
+      <c r="B45">
+        <v>7</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>3</v>
+      </c>
+      <c r="E45">
+        <v>2</v>
+      </c>
+      <c r="F45">
+        <v>22.69</v>
+      </c>
+      <c r="G45">
+        <v>25</v>
+      </c>
+      <c r="H45">
+        <v>100</v>
+      </c>
+      <c r="I45">
+        <v>0.99</v>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46">
+        <v>31</v>
+      </c>
+      <c r="B46">
+        <v>7</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>3</v>
+      </c>
+      <c r="E46">
+        <v>2</v>
+      </c>
+      <c r="F46">
+        <v>22.93</v>
+      </c>
+      <c r="G46">
+        <v>23</v>
+      </c>
+      <c r="H46">
+        <v>100</v>
+      </c>
+      <c r="I46">
+        <v>0.999</v>
+      </c>
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47">
+        <v>32</v>
+      </c>
+      <c r="B47">
+        <v>7</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>3</v>
+      </c>
+      <c r="F47">
+        <v>21.34</v>
+      </c>
+      <c r="G47">
+        <v>47</v>
+      </c>
+      <c r="H47">
+        <v>97.62</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48">
+        <v>33</v>
+      </c>
+      <c r="B48">
+        <v>7</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>3</v>
+      </c>
+      <c r="E48">
+        <v>3</v>
+      </c>
+      <c r="F48">
+        <v>21.04</v>
+      </c>
+      <c r="G48">
+        <v>32</v>
+      </c>
+      <c r="H48">
+        <v>98.98</v>
+      </c>
+      <c r="I48">
+        <v>0.9</v>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49">
+        <v>34</v>
+      </c>
+      <c r="B49">
+        <v>7</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>3</v>
+      </c>
+      <c r="E49">
+        <v>3</v>
+      </c>
+      <c r="F49">
+        <v>22.74</v>
+      </c>
+      <c r="G49">
+        <v>21</v>
+      </c>
+      <c r="H49">
+        <v>100</v>
+      </c>
+      <c r="I49">
+        <v>0.99</v>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50">
+        <v>35</v>
+      </c>
+      <c r="B50">
+        <v>7</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <v>3</v>
+      </c>
+      <c r="E50">
+        <v>3</v>
+      </c>
+      <c r="F50">
+        <v>22.83</v>
+      </c>
+      <c r="G50">
+        <v>24</v>
+      </c>
+      <c r="H50">
+        <v>100</v>
+      </c>
+      <c r="I50">
+        <v>0.999</v>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51">
+        <v>36</v>
+      </c>
+      <c r="B51">
+        <v>7</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>3</v>
+      </c>
+      <c r="E51">
+        <v>4</v>
+      </c>
+      <c r="F51">
+        <v>21.18</v>
+      </c>
+      <c r="G51">
+        <v>49</v>
+      </c>
+      <c r="H51">
+        <v>96.66</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52">
+        <v>37</v>
+      </c>
+      <c r="B52">
+        <v>7</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>3</v>
+      </c>
+      <c r="E52">
+        <v>4</v>
+      </c>
+      <c r="F52">
+        <v>20.65</v>
+      </c>
+      <c r="G52">
+        <v>30</v>
+      </c>
+      <c r="H52">
+        <v>98.54</v>
+      </c>
+      <c r="I52">
+        <v>0.9</v>
+      </c>
+      <c r="J52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53">
+        <v>38</v>
+      </c>
+      <c r="B53">
+        <v>7</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>3</v>
+      </c>
+      <c r="E53">
+        <v>4</v>
+      </c>
+      <c r="F53">
+        <v>23.08</v>
+      </c>
+      <c r="G53">
+        <v>22</v>
+      </c>
+      <c r="H53">
+        <v>100</v>
+      </c>
+      <c r="I53">
+        <v>0.99</v>
+      </c>
+      <c r="J53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54">
+        <v>39</v>
+      </c>
+      <c r="B54">
+        <v>7</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>3</v>
+      </c>
+      <c r="E54">
+        <v>4</v>
+      </c>
+      <c r="F54">
+        <v>22.98</v>
+      </c>
+      <c r="G54">
+        <v>20</v>
+      </c>
+      <c r="H54">
+        <v>100</v>
+      </c>
+      <c r="I54">
+        <v>0.999</v>
+      </c>
+      <c r="J54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55">
+        <v>40</v>
+      </c>
+      <c r="B55">
+        <v>7</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>3</v>
+      </c>
+      <c r="E55">
+        <v>5</v>
+      </c>
+      <c r="F55">
+        <v>21.42</v>
+      </c>
+      <c r="G55">
+        <v>54</v>
+      </c>
+      <c r="H55">
+        <v>96.75</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56">
+        <v>41</v>
+      </c>
+      <c r="B56">
+        <v>7</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>3</v>
+      </c>
+      <c r="E56">
+        <v>5</v>
+      </c>
+      <c r="F56">
+        <v>20.62</v>
+      </c>
+      <c r="G56">
+        <v>35</v>
+      </c>
+      <c r="H56">
+        <v>98.76</v>
+      </c>
+      <c r="I56">
+        <v>0.9</v>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57">
+        <v>42</v>
+      </c>
+      <c r="B57">
+        <v>7</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>3</v>
+      </c>
+      <c r="E57">
+        <v>5</v>
+      </c>
+      <c r="F57">
+        <v>22.82</v>
+      </c>
+      <c r="G57">
+        <v>22</v>
+      </c>
+      <c r="H57">
+        <v>100</v>
+      </c>
+      <c r="I57">
+        <v>0.99</v>
+      </c>
+      <c r="J57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58">
+        <v>43</v>
+      </c>
+      <c r="B58">
+        <v>7</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>3</v>
+      </c>
+      <c r="E58">
+        <v>5</v>
+      </c>
+      <c r="F58">
+        <v>22.9</v>
+      </c>
+      <c r="G58">
+        <v>20</v>
+      </c>
+      <c r="H58">
+        <v>100</v>
+      </c>
+      <c r="I58">
+        <v>0.999</v>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59">
+        <v>44</v>
+      </c>
+      <c r="B59">
+        <v>7</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>5</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+      <c r="F59">
+        <v>20.3</v>
+      </c>
+      <c r="G59">
+        <v>50</v>
+      </c>
+      <c r="H59">
+        <v>94.33</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60">
+        <v>45</v>
+      </c>
+      <c r="B60">
+        <v>7</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>5</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+      <c r="F60">
+        <v>21.35</v>
+      </c>
+      <c r="G60">
+        <v>27</v>
+      </c>
+      <c r="H60">
+        <v>99.38</v>
+      </c>
+      <c r="I60">
+        <v>0.9</v>
+      </c>
+      <c r="J60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61">
+        <v>46</v>
+      </c>
+      <c r="B61">
+        <v>7</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>5</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <v>22.92</v>
+      </c>
+      <c r="G61">
+        <v>21</v>
+      </c>
+      <c r="H61">
+        <v>100</v>
+      </c>
+      <c r="I61">
+        <v>0.99</v>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62">
+        <v>47</v>
+      </c>
+      <c r="B62">
+        <v>7</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>5</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <v>22.97</v>
+      </c>
+      <c r="G62">
+        <v>21</v>
+      </c>
+      <c r="H62">
+        <v>100</v>
+      </c>
+      <c r="I62">
+        <v>0.999</v>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63">
+        <v>48</v>
+      </c>
+      <c r="B63">
+        <v>7</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>5</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+      <c r="F63">
+        <v>22.77</v>
+      </c>
+      <c r="G63">
+        <v>21</v>
+      </c>
+      <c r="H63">
+        <v>100</v>
+      </c>
+      <c r="I63">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64">
+        <v>49</v>
+      </c>
+      <c r="B64">
+        <v>7</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>5</v>
+      </c>
+      <c r="E64">
+        <v>2</v>
+      </c>
+      <c r="F64">
+        <v>20.52</v>
+      </c>
+      <c r="G64" s="2">
+        <v>60</v>
+      </c>
+      <c r="H64">
+        <v>91.96</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65">
+        <v>50</v>
+      </c>
+      <c r="B65">
+        <v>7</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>5</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
+      </c>
+      <c r="F65">
+        <v>20.010000000000002</v>
+      </c>
+      <c r="G65">
+        <v>37</v>
+      </c>
+      <c r="H65">
+        <v>97.84</v>
+      </c>
+      <c r="I65">
+        <v>0.9</v>
+      </c>
+      <c r="J65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66">
+        <v>51</v>
+      </c>
+      <c r="B66">
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>5</v>
+      </c>
+      <c r="E66">
+        <v>2</v>
+      </c>
+      <c r="F66">
+        <v>22.99</v>
+      </c>
+      <c r="G66">
+        <v>22</v>
+      </c>
+      <c r="H66">
+        <v>100</v>
+      </c>
+      <c r="I66">
+        <v>0.99</v>
+      </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67">
+        <v>52</v>
+      </c>
+      <c r="B67">
+        <v>7</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>5</v>
+      </c>
+      <c r="E67">
+        <v>2</v>
+      </c>
+      <c r="F67">
+        <v>23.07</v>
+      </c>
+      <c r="G67">
+        <v>22</v>
+      </c>
+      <c r="H67">
+        <v>100</v>
+      </c>
+      <c r="I67">
+        <v>0.999</v>
+      </c>
+      <c r="J67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68">
+        <v>53</v>
+      </c>
+      <c r="B68">
+        <v>7</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>5</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="F68">
+        <v>22.96</v>
+      </c>
+      <c r="G68">
+        <v>20</v>
+      </c>
+      <c r="H68">
+        <v>100</v>
+      </c>
+      <c r="I68">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="J68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69">
+        <v>54</v>
+      </c>
+      <c r="B69">
+        <v>7</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>5</v>
+      </c>
+      <c r="E69">
+        <v>3</v>
+      </c>
+      <c r="F69">
+        <v>20.72</v>
+      </c>
+      <c r="G69">
+        <v>59</v>
+      </c>
+      <c r="H69">
+        <v>91.48</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70">
+        <v>55</v>
+      </c>
+      <c r="B70">
+        <v>7</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>5</v>
+      </c>
+      <c r="E70">
+        <v>3</v>
+      </c>
+      <c r="F70">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="G70">
+        <v>40</v>
+      </c>
+      <c r="H70">
+        <v>96.99</v>
+      </c>
+      <c r="I70">
+        <v>0.9</v>
+      </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71">
+        <v>56</v>
+      </c>
+      <c r="B71">
+        <v>7</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>5</v>
+      </c>
+      <c r="E71">
+        <v>3</v>
+      </c>
+      <c r="F71">
+        <v>22.84</v>
+      </c>
+      <c r="G71">
+        <v>23</v>
+      </c>
+      <c r="H71">
+        <v>100</v>
+      </c>
+      <c r="I71">
+        <v>0.99</v>
+      </c>
+      <c r="J71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72">
+        <v>57</v>
+      </c>
+      <c r="B72">
+        <v>7</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>5</v>
+      </c>
+      <c r="E72">
+        <v>3</v>
+      </c>
+      <c r="F72">
+        <v>22.68</v>
+      </c>
+      <c r="G72">
+        <v>20</v>
+      </c>
+      <c r="H72">
+        <v>100</v>
+      </c>
+      <c r="I72">
+        <v>0.999</v>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73">
+        <v>58</v>
+      </c>
+      <c r="B73">
+        <v>7</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>5</v>
+      </c>
+      <c r="E73">
+        <v>3</v>
+      </c>
+      <c r="F73">
+        <v>22.92</v>
+      </c>
+      <c r="G73">
+        <v>19</v>
+      </c>
+      <c r="H73">
+        <v>100</v>
+      </c>
+      <c r="I73">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74">
+        <v>59</v>
+      </c>
+      <c r="B74">
+        <v>7</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>5</v>
+      </c>
+      <c r="E74">
+        <v>4</v>
+      </c>
+      <c r="F74">
+        <v>20.48</v>
+      </c>
+      <c r="G74">
+        <v>59</v>
+      </c>
+      <c r="H74">
+        <v>86.84</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75">
+        <v>60</v>
+      </c>
+      <c r="B75">
+        <v>7</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>5</v>
+      </c>
+      <c r="E75">
+        <v>4</v>
+      </c>
+      <c r="F75">
+        <v>19.45</v>
+      </c>
+      <c r="G75">
+        <v>39</v>
+      </c>
+      <c r="H75">
+        <v>96.41</v>
+      </c>
+      <c r="I75">
+        <v>0.9</v>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76">
+        <v>61</v>
+      </c>
+      <c r="B76">
+        <v>7</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>5</v>
+      </c>
+      <c r="E76">
+        <v>4</v>
+      </c>
+      <c r="F76">
+        <v>22.83</v>
+      </c>
+      <c r="G76">
+        <v>23</v>
+      </c>
+      <c r="H76">
+        <v>100</v>
+      </c>
+      <c r="I76">
+        <v>0.99</v>
+      </c>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77">
+        <v>62</v>
+      </c>
+      <c r="B77">
+        <v>7</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>5</v>
+      </c>
+      <c r="E77">
+        <v>4</v>
+      </c>
+      <c r="F77">
+        <v>23.03</v>
+      </c>
+      <c r="G77">
+        <v>21</v>
+      </c>
+      <c r="H77">
+        <v>100</v>
+      </c>
+      <c r="I77">
+        <v>0.999</v>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78">
+        <v>63</v>
+      </c>
+      <c r="B78">
+        <v>7</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>5</v>
+      </c>
+      <c r="E78">
+        <v>4</v>
+      </c>
+      <c r="F78">
+        <v>22.8</v>
+      </c>
+      <c r="G78">
+        <v>19</v>
+      </c>
+      <c r="H78">
+        <v>100</v>
+      </c>
+      <c r="I78">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="J78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79">
+        <v>64</v>
+      </c>
+      <c r="B79">
+        <v>7</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>5</v>
+      </c>
+      <c r="E79">
+        <v>5</v>
+      </c>
+      <c r="F79">
+        <v>20.04</v>
+      </c>
+      <c r="G79">
+        <v>60</v>
+      </c>
+      <c r="H79">
+        <v>84</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80">
+        <v>65</v>
+      </c>
+      <c r="B80">
+        <v>7</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>5</v>
+      </c>
+      <c r="E80">
+        <v>5</v>
+      </c>
+      <c r="F80">
+        <v>19.7</v>
+      </c>
+      <c r="G80">
+        <v>42</v>
+      </c>
+      <c r="H80">
+        <v>95.54</v>
+      </c>
+      <c r="I80">
+        <v>0.9</v>
+      </c>
+      <c r="J80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10">
+      <c r="A81">
+        <v>66</v>
+      </c>
+      <c r="B81">
+        <v>7</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <v>5</v>
+      </c>
+      <c r="E81">
+        <v>5</v>
+      </c>
+      <c r="F81">
+        <v>23.08</v>
+      </c>
+      <c r="G81">
+        <v>23</v>
+      </c>
+      <c r="H81">
+        <v>100</v>
+      </c>
+      <c r="I81">
+        <v>0.99</v>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10">
+      <c r="A82">
+        <v>67</v>
+      </c>
+      <c r="B82">
+        <v>7</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>5</v>
+      </c>
+      <c r="E82">
+        <v>5</v>
+      </c>
+      <c r="F82">
+        <v>22.84</v>
+      </c>
+      <c r="G82">
+        <v>20</v>
+      </c>
+      <c r="H82">
+        <v>100</v>
+      </c>
+      <c r="I82">
+        <v>0.999</v>
+      </c>
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10">
+      <c r="A83">
+        <v>68</v>
+      </c>
+      <c r="B83">
+        <v>7</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <v>5</v>
+      </c>
+      <c r="E83">
+        <v>5</v>
+      </c>
+      <c r="F83">
+        <v>22.86</v>
+      </c>
+      <c r="G83">
+        <v>19</v>
+      </c>
+      <c r="H83">
+        <v>100</v>
+      </c>
+      <c r="I83">
+        <v>0.99990000000000001</v>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10">
+      <c r="A84">
+        <v>69</v>
+      </c>
+      <c r="B84">
+        <v>7</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10">
+      <c r="A85">
+        <v>70</v>
+      </c>
+      <c r="B85">
+        <v>7</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10">
+      <c r="A86">
+        <v>71</v>
+      </c>
+      <c r="B86">
+        <v>7</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10">
+      <c r="A87">
+        <v>72</v>
+      </c>
+      <c r="B87">
+        <v>7</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10">
+      <c r="A88">
+        <v>73</v>
+      </c>
+      <c r="B88">
+        <v>7</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10">
+      <c r="A89">
+        <v>74</v>
+      </c>
+      <c r="B89">
+        <v>7</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10">
+      <c r="A90">
+        <v>75</v>
+      </c>
+      <c r="B90">
+        <v>7</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10">
+      <c r="A91">
+        <v>76</v>
+      </c>
+      <c r="B91">
+        <v>7</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10">
+      <c r="A92">
+        <v>77</v>
+      </c>
+      <c r="B92">
+        <v>7</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10">
+      <c r="A93">
+        <v>78</v>
+      </c>
+      <c r="B93">
+        <v>7</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10">
+      <c r="A94">
+        <v>79</v>
+      </c>
+      <c r="B94">
+        <v>7</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10">
+      <c r="A95">
+        <v>80</v>
+      </c>
+      <c r="B95">
+        <v>7</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10">
+      <c r="A96">
+        <v>81</v>
+      </c>
+      <c r="B96">
+        <v>7</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97">
+        <v>82</v>
+      </c>
+      <c r="B97">
+        <v>7</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98">
+        <v>83</v>
+      </c>
+      <c r="B98">
+        <v>7</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99">
+        <v>84</v>
+      </c>
+      <c r="B99">
+        <v>7</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100">
+        <v>85</v>
+      </c>
+      <c r="B100">
+        <v>7</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101">
+        <v>86</v>
+      </c>
+      <c r="B101">
+        <v>7</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102">
+        <v>87</v>
+      </c>
+      <c r="B102">
+        <v>7</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103">
+        <v>88</v>
+      </c>
+      <c r="B103">
+        <v>7</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104">
+        <v>89</v>
+      </c>
+      <c r="B104">
+        <v>7</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105">
+        <v>90</v>
+      </c>
+      <c r="B105">
+        <v>7</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106">
+        <v>91</v>
+      </c>
+      <c r="B106">
+        <v>7</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107">
+        <v>92</v>
+      </c>
+      <c r="B107">
+        <v>7</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108">
+        <v>93</v>
+      </c>
+      <c r="B108">
+        <v>7</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109">
+        <v>94</v>
+      </c>
+      <c r="B109">
+        <v>7</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110">
+        <v>95</v>
+      </c>
+      <c r="B110">
+        <v>7</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111">
+        <v>96</v>
+      </c>
+      <c r="B111">
+        <v>7</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112">
+        <v>97</v>
+      </c>
+      <c r="B112">
+        <v>7</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113">
+        <v>98</v>
+      </c>
+      <c r="B113">
+        <v>7</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114">
+        <v>99</v>
+      </c>
+      <c r="B114">
+        <v>7</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115">
+        <v>100</v>
+      </c>
+      <c r="B115">
+        <v>7</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116">
+        <v>101</v>
+      </c>
+      <c r="B116">
+        <v>7</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118">
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AFB62DF-B5AA-5E4C-80E6-11565E9C9DBC}">
+  <dimension ref="A1:Q34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:17">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J2" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>57.99</v>
+      </c>
+      <c r="G3">
+        <v>42</v>
+      </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M3" t="s">
+        <v>1</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
+      <c r="P3" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>59.33</v>
+      </c>
+      <c r="G4">
+        <v>20</v>
+      </c>
+      <c r="H4">
+        <v>100</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>50</v>
+      </c>
+      <c r="M4">
+        <v>0.1</v>
+      </c>
+      <c r="N4">
+        <v>56.39</v>
+      </c>
+      <c r="P4">
+        <v>0.1</v>
+      </c>
+      <c r="Q4">
+        <v>58.37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>59.53</v>
+      </c>
+      <c r="G5">
+        <v>22</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
+        <v>50</v>
+      </c>
+      <c r="M5">
+        <v>0.2</v>
+      </c>
+      <c r="N5">
+        <v>56.94</v>
+      </c>
+      <c r="P5">
+        <v>0.2</v>
+      </c>
+      <c r="Q5">
+        <v>58.81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>59.99</v>
+      </c>
+      <c r="G6">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6">
+        <v>0.3</v>
+      </c>
+      <c r="N6">
+        <v>57.27</v>
+      </c>
+      <c r="P6">
+        <v>0.3</v>
+      </c>
+      <c r="Q6">
+        <v>58.84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>59.95</v>
+      </c>
+      <c r="G7">
+        <v>14</v>
+      </c>
+      <c r="H7">
+        <v>100</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7">
+        <v>0.4</v>
+      </c>
+      <c r="P7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>60.24</v>
+      </c>
+      <c r="G8">
+        <v>16</v>
+      </c>
+      <c r="H8">
+        <v>100</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8">
+        <v>0.5</v>
+      </c>
+      <c r="P8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>60.28</v>
+      </c>
+      <c r="G9" s="1">
+        <v>13</v>
+      </c>
+      <c r="H9" s="1">
+        <v>100</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>60.09</v>
+      </c>
+      <c r="G10">
+        <v>14</v>
+      </c>
+      <c r="H10">
+        <v>100</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16">
+        <v>1</v>
+      </c>
+      <c r="B16">
+        <v>8</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>59.76</v>
+      </c>
+      <c r="G16">
+        <v>15</v>
+      </c>
+      <c r="H16">
+        <v>100</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>60.1</v>
+      </c>
+      <c r="G17">
+        <v>24</v>
+      </c>
+      <c r="H17">
+        <v>100</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18">
+        <v>3</v>
+      </c>
+      <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>60.07</v>
+      </c>
+      <c r="G18">
+        <v>21</v>
+      </c>
+      <c r="H18">
+        <v>100</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19">
+        <v>4</v>
+      </c>
+      <c r="B19">
+        <v>8</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>60.05</v>
+      </c>
+      <c r="G19">
+        <v>16</v>
+      </c>
+      <c r="H19">
+        <v>100</v>
+      </c>
+      <c r="I19">
+        <v>0.9</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20">
+        <v>8</v>
+      </c>
+      <c r="C20">
+        <v>0</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>59.85</v>
+      </c>
+      <c r="G20">
+        <v>16</v>
+      </c>
+      <c r="H20">
+        <v>100</v>
+      </c>
+      <c r="I20">
+        <v>0.99</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21">
+        <v>6</v>
+      </c>
+      <c r="B21">
+        <v>8</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>60.11</v>
+      </c>
+      <c r="G21">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>100</v>
+      </c>
+      <c r="I21">
+        <v>0.999</v>
+      </c>
+      <c r="J21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22">
+        <v>7</v>
+      </c>
+      <c r="B22">
+        <v>8</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="F22">
+        <v>60.82</v>
+      </c>
+      <c r="G22">
+        <v>28</v>
+      </c>
+      <c r="H22">
+        <v>100</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23">
+        <v>8</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="F23">
+        <v>60.65</v>
+      </c>
+      <c r="G23">
+        <v>24</v>
+      </c>
+      <c r="H23">
+        <v>100</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24">
+        <v>9</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>4</v>
+      </c>
+      <c r="F24">
+        <v>60.97</v>
+      </c>
+      <c r="G24">
+        <v>21</v>
+      </c>
+      <c r="H24">
+        <v>100</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25">
+        <v>10</v>
+      </c>
+      <c r="B25">
+        <v>8</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>5</v>
+      </c>
+      <c r="F25" s="3">
+        <v>61.37</v>
+      </c>
+      <c r="G25">
+        <v>31</v>
+      </c>
+      <c r="H25">
+        <v>100</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>8</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26">
+        <v>60.95</v>
+      </c>
+      <c r="G26">
+        <v>33</v>
+      </c>
+      <c r="H26">
+        <v>100</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27">
+        <v>12</v>
+      </c>
+      <c r="B27">
+        <v>8</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>10</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>61.15</v>
+      </c>
+      <c r="H27">
+        <v>100</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8EB3395-ED30-6A4D-9E8A-D7B1C51FA28D}">
+  <dimension ref="A1:M111"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>19.09</v>
+      </c>
+      <c r="D5">
+        <v>30</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>19.09</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>18.559999999999999</v>
+      </c>
+      <c r="D8">
+        <v>33</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>18</v>
+      </c>
+      <c r="D9">
+        <v>23</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>18.14</v>
+      </c>
+      <c r="D10">
+        <v>26</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+      <c r="C11">
+        <v>17.940000000000001</v>
+      </c>
+      <c r="D11">
+        <v>34</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>18.37</v>
+      </c>
+      <c r="D12">
+        <v>42</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>18.57</v>
+      </c>
+      <c r="D13">
+        <v>30</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14">
+        <v>6</v>
+      </c>
+      <c r="B14">
+        <v>5</v>
+      </c>
+      <c r="C14">
+        <v>18.27</v>
+      </c>
+      <c r="D14">
+        <v>31</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15">
+        <v>6</v>
+      </c>
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>18.63</v>
+      </c>
+      <c r="D15">
+        <v>35</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16">
+        <v>6</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="D16">
+        <v>28</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="B24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" t="s">
+        <v>39</v>
+      </c>
+      <c r="F24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" t="s">
+        <v>41</v>
+      </c>
+      <c r="I24" t="s">
+        <v>49</v>
+      </c>
+      <c r="J24" t="s">
+        <v>54</v>
+      </c>
+      <c r="K24" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25">
+        <v>1</v>
+      </c>
+      <c r="B25" s="1">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1">
+        <v>0</v>
+      </c>
+      <c r="D25" s="1">
+        <v>0</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1">
+        <v>18.829999999999998</v>
+      </c>
+      <c r="G25" s="1">
+        <v>31</v>
+      </c>
+      <c r="H25">
+        <v>100</v>
+      </c>
+      <c r="I25" t="s">
+        <v>50</v>
+      </c>
+      <c r="J25" t="s">
+        <v>50</v>
+      </c>
+      <c r="K25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26">
+        <v>2</v>
+      </c>
+      <c r="B26">
+        <v>6</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>5</v>
+      </c>
+      <c r="E26">
+        <v>5</v>
+      </c>
+      <c r="F26">
+        <v>17.64</v>
+      </c>
+      <c r="G26">
+        <v>94</v>
+      </c>
+      <c r="H26">
+        <v>96</v>
+      </c>
+      <c r="I26" t="s">
+        <v>50</v>
+      </c>
+      <c r="J26" t="s">
+        <v>50</v>
+      </c>
+      <c r="K26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27">
+        <v>3</v>
+      </c>
+      <c r="B27">
+        <v>6</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27">
+        <v>17.57</v>
+      </c>
+      <c r="G27">
+        <v>91</v>
+      </c>
+      <c r="H27">
+        <v>97.22</v>
+      </c>
+      <c r="I27" t="s">
+        <v>50</v>
+      </c>
+      <c r="J27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28">
+        <v>4</v>
+      </c>
+      <c r="B28" s="1">
+        <v>6</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0</v>
+      </c>
+      <c r="D28" s="1">
+        <v>5</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1">
+        <v>18.18</v>
+      </c>
+      <c r="G28" s="1">
+        <v>28</v>
+      </c>
+      <c r="H28">
+        <v>100</v>
+      </c>
+      <c r="I28" t="s">
+        <v>50</v>
+      </c>
+      <c r="J28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29">
+        <v>5</v>
+      </c>
+      <c r="B29">
+        <v>6</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+      <c r="F29">
+        <v>17.43</v>
+      </c>
+      <c r="G29">
+        <v>38</v>
+      </c>
+      <c r="H29">
+        <v>100</v>
+      </c>
+      <c r="I29" t="s">
+        <v>50</v>
+      </c>
+      <c r="J29" t="s">
+        <v>50</v>
+      </c>
+      <c r="K29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30">
+        <v>6</v>
+      </c>
+      <c r="B30">
+        <v>6</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+      <c r="F30">
+        <v>18.809999999999999</v>
+      </c>
+      <c r="G30">
+        <v>27</v>
+      </c>
+      <c r="H30">
+        <v>100</v>
+      </c>
+      <c r="I30" t="s">
+        <v>50</v>
+      </c>
+      <c r="J30" t="s">
+        <v>50</v>
+      </c>
+      <c r="K30" t="s">
+        <v>46</v>
+      </c>
+      <c r="M30" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31">
+        <v>7</v>
+      </c>
+      <c r="B31">
+        <v>6</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>10</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>15.91</v>
+      </c>
+      <c r="G31">
+        <v>32</v>
+      </c>
+      <c r="H31">
+        <v>100</v>
+      </c>
+      <c r="I31" t="s">
+        <v>50</v>
+      </c>
+      <c r="J31" t="s">
+        <v>50</v>
+      </c>
+      <c r="K31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32">
+        <v>8</v>
+      </c>
+      <c r="B32">
+        <v>6</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>5</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>16.54</v>
+      </c>
+      <c r="G32">
+        <v>29</v>
+      </c>
+      <c r="H32">
+        <v>100</v>
+      </c>
+      <c r="I32" t="s">
+        <v>50</v>
+      </c>
+      <c r="J32" t="s">
+        <v>50</v>
+      </c>
+      <c r="K32" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33">
+        <v>9</v>
+      </c>
+      <c r="B33">
+        <v>6</v>
+      </c>
+      <c r="C33">
+        <v>0</v>
+      </c>
+      <c r="D33">
+        <v>24</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>16.95</v>
+      </c>
+      <c r="G33">
+        <v>41</v>
+      </c>
+      <c r="H33">
+        <v>100</v>
+      </c>
+      <c r="I33" t="s">
+        <v>50</v>
+      </c>
+      <c r="J33" t="s">
+        <v>50</v>
+      </c>
+      <c r="K33" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34">
+        <v>10</v>
+      </c>
+      <c r="J34" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35">
+        <v>11</v>
+      </c>
+      <c r="J35" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36">
+        <v>12</v>
+      </c>
+      <c r="B36">
+        <v>6</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+      <c r="F36">
+        <v>18.7</v>
+      </c>
+      <c r="G36">
+        <v>26</v>
+      </c>
+      <c r="H36">
+        <v>100</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36" t="s">
+        <v>50</v>
+      </c>
+      <c r="K36" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37">
+        <v>13</v>
+      </c>
+      <c r="B37">
+        <v>6</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <v>5</v>
+      </c>
+      <c r="E37">
+        <v>5</v>
+      </c>
+      <c r="F37">
+        <v>18.22</v>
+      </c>
+      <c r="G37">
+        <v>27</v>
+      </c>
+      <c r="H37">
+        <v>100</v>
+      </c>
+      <c r="I37">
+        <v>0.999</v>
+      </c>
+      <c r="J37" t="s">
+        <v>50</v>
+      </c>
+      <c r="K37" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38">
+        <v>14</v>
+      </c>
+      <c r="B38">
+        <v>6</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <v>5</v>
+      </c>
+      <c r="E38">
+        <v>5</v>
+      </c>
+      <c r="F38">
+        <v>18.16</v>
+      </c>
+      <c r="G38">
+        <v>31</v>
+      </c>
+      <c r="H38">
+        <v>100</v>
+      </c>
+      <c r="I38">
+        <v>0.99</v>
+      </c>
+      <c r="J38" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39">
+        <v>15</v>
+      </c>
+      <c r="B39">
+        <v>6</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <v>18.809999999999999</v>
+      </c>
+      <c r="G39">
+        <v>26</v>
+      </c>
+      <c r="H39">
+        <v>100</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39" t="s">
+        <v>50</v>
+      </c>
+      <c r="K39" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40">
+        <v>16</v>
+      </c>
+      <c r="B40">
+        <v>6</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>18.690000000000001</v>
+      </c>
+      <c r="G40">
+        <v>33</v>
+      </c>
+      <c r="H40">
+        <v>100</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41">
+        <v>17</v>
+      </c>
+      <c r="B41">
+        <v>6</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>18.829999999999998</v>
+      </c>
+      <c r="G41">
+        <v>31</v>
+      </c>
+      <c r="H41">
+        <v>100</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42">
+        <v>18</v>
+      </c>
+      <c r="B42">
+        <v>6</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>18.72</v>
+      </c>
+      <c r="G42">
+        <v>34</v>
+      </c>
+      <c r="H42">
+        <v>100</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43">
+        <v>19</v>
+      </c>
+      <c r="B43">
+        <v>6</v>
+      </c>
+      <c r="C43">
+        <v>0.1</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>18.75</v>
+      </c>
+      <c r="G43">
+        <v>33</v>
+      </c>
+      <c r="H43">
+        <v>100</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44">
+        <v>20</v>
+      </c>
+      <c r="B44">
+        <v>6</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>18.77</v>
+      </c>
+      <c r="G44">
+        <v>31</v>
+      </c>
+      <c r="H44">
+        <v>100</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45">
+        <v>21</v>
+      </c>
+      <c r="B45">
+        <v>6</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45" s="3">
+        <v>18.89</v>
+      </c>
+      <c r="G45">
+        <v>33</v>
+      </c>
+      <c r="H45">
+        <v>100</v>
+      </c>
+      <c r="I45">
+        <v>0.99</v>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46">
+        <v>22</v>
+      </c>
+      <c r="B46">
+        <v>6</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46">
+        <v>18.77</v>
+      </c>
+      <c r="G46">
+        <v>30</v>
+      </c>
+      <c r="H46">
+        <v>100</v>
+      </c>
+      <c r="I46">
+        <v>0.9</v>
+      </c>
+      <c r="J46" t="b">
+        <v>0</v>
+      </c>
+      <c r="K46" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47">
+        <v>23</v>
+      </c>
+      <c r="B47">
+        <v>6</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>18.77</v>
+      </c>
+      <c r="G47">
+        <v>29</v>
+      </c>
+      <c r="H47">
+        <v>100</v>
+      </c>
+      <c r="I47">
+        <v>0.999</v>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S60"/>
+  <dimension ref="A1:X72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -898,7 +6338,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:24">
       <c r="A33">
         <v>7</v>
       </c>
@@ -912,7 +6352,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:24">
       <c r="A34">
         <v>7</v>
       </c>
@@ -923,7 +6363,7 @@
         <v>56.66</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:24">
       <c r="A35">
         <v>7</v>
       </c>
@@ -937,7 +6377,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:24">
       <c r="B37" t="s">
         <v>19</v>
       </c>
@@ -951,7 +6391,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:24">
       <c r="A38" t="s">
         <v>20</v>
       </c>
@@ -962,15 +6402,21 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:24">
       <c r="J39" t="s">
         <v>25</v>
       </c>
       <c r="P39" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="40" spans="1:19">
+      <c r="U39" t="s">
+        <v>26</v>
+      </c>
+      <c r="V39" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24">
       <c r="A40" t="s">
         <v>1</v>
       </c>
@@ -1007,8 +6453,20 @@
       <c r="S40" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="41" spans="1:19">
+      <c r="U40" t="s">
+        <v>1</v>
+      </c>
+      <c r="V40" t="s">
+        <v>6</v>
+      </c>
+      <c r="W40" t="s">
+        <v>27</v>
+      </c>
+      <c r="X40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24">
       <c r="J41">
         <v>0</v>
       </c>
@@ -1024,8 +6482,20 @@
       <c r="Q41">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="1:19">
+      <c r="U41">
+        <v>6</v>
+      </c>
+      <c r="V41">
+        <v>5</v>
+      </c>
+      <c r="W41">
+        <v>18.5</v>
+      </c>
+      <c r="X41">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24">
       <c r="J42">
         <v>1</v>
       </c>
@@ -1047,8 +6517,20 @@
       <c r="S42">
         <v>219</v>
       </c>
-    </row>
-    <row r="43" spans="1:19">
+      <c r="U42">
+        <v>7</v>
+      </c>
+      <c r="V42">
+        <v>5</v>
+      </c>
+      <c r="W42" s="3">
+        <v>18.96</v>
+      </c>
+      <c r="X42">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24">
       <c r="J43">
         <v>2</v>
       </c>
@@ -1068,7 +6550,7 @@
         <v>17.82</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:24">
       <c r="J44">
         <v>3</v>
       </c>
@@ -1088,7 +6570,7 @@
         <v>18.04</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:24">
       <c r="J45">
         <v>4</v>
       </c>
@@ -1108,7 +6590,7 @@
         <v>18.09</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:24">
       <c r="J46">
         <v>5</v>
       </c>
@@ -1128,7 +6610,7 @@
         <v>18.14</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:24">
       <c r="J47">
         <v>6</v>
       </c>
@@ -1151,7 +6633,7 @@
         <v>18.55</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:24">
       <c r="J48">
         <v>7</v>
       </c>
@@ -1250,6 +6732,9 @@
       <c r="L52" t="s">
         <v>27</v>
       </c>
+      <c r="M52" t="s">
+        <v>23</v>
+      </c>
       <c r="P52" t="s">
         <v>1</v>
       </c>
@@ -1355,6 +6840,12 @@
       <c r="Q58">
         <v>5</v>
       </c>
+      <c r="R58">
+        <v>18.52</v>
+      </c>
+      <c r="S58">
+        <v>105</v>
+      </c>
     </row>
     <row r="59" spans="1:19">
       <c r="J59">
@@ -1363,13 +6854,19 @@
       <c r="K59">
         <v>5</v>
       </c>
+      <c r="L59">
+        <v>18.77</v>
+      </c>
+      <c r="M59">
+        <v>38</v>
+      </c>
       <c r="P59">
         <v>7</v>
       </c>
       <c r="Q59">
         <v>5</v>
       </c>
-      <c r="R59">
+      <c r="R59" s="3">
         <v>19.010000000000002</v>
       </c>
     </row>
@@ -1380,6 +6877,12 @@
       <c r="K60">
         <v>5</v>
       </c>
+      <c r="L60">
+        <v>18.89</v>
+      </c>
+      <c r="M60">
+        <v>34</v>
+      </c>
       <c r="P60">
         <v>8</v>
       </c>
@@ -1388,6 +6891,167 @@
       </c>
       <c r="R60">
         <v>18.63</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19">
+      <c r="J62" t="s">
+        <v>16</v>
+      </c>
+      <c r="P62" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19">
+      <c r="J63" t="s">
+        <v>1</v>
+      </c>
+      <c r="K63" t="s">
+        <v>6</v>
+      </c>
+      <c r="L63" t="s">
+        <v>27</v>
+      </c>
+      <c r="M63" t="s">
+        <v>23</v>
+      </c>
+      <c r="P63" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>6</v>
+      </c>
+      <c r="R63" t="s">
+        <v>27</v>
+      </c>
+      <c r="S63" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19">
+      <c r="J64">
+        <v>5</v>
+      </c>
+      <c r="K64">
+        <v>5</v>
+      </c>
+      <c r="P64">
+        <v>6</v>
+      </c>
+      <c r="Q64">
+        <v>5</v>
+      </c>
+      <c r="R64">
+        <v>17.96</v>
+      </c>
+      <c r="S64">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="65" spans="10:19">
+      <c r="J65">
+        <v>6</v>
+      </c>
+      <c r="K65">
+        <v>5</v>
+      </c>
+      <c r="L65">
+        <v>18.79</v>
+      </c>
+      <c r="M65">
+        <v>32</v>
+      </c>
+      <c r="P65">
+        <v>6</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>19.11</v>
+      </c>
+      <c r="S65">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="66" spans="10:19">
+      <c r="J66">
+        <v>7</v>
+      </c>
+      <c r="K66">
+        <v>5</v>
+      </c>
+      <c r="L66">
+        <v>18.86</v>
+      </c>
+      <c r="M66">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="67" spans="10:19">
+      <c r="J67">
+        <v>8</v>
+      </c>
+      <c r="K67">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="10:19">
+      <c r="J69" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="70" spans="10:19">
+      <c r="J70" t="s">
+        <v>1</v>
+      </c>
+      <c r="K70" t="s">
+        <v>6</v>
+      </c>
+      <c r="L70" t="s">
+        <v>27</v>
+      </c>
+      <c r="M70" t="s">
+        <v>23</v>
+      </c>
+      <c r="N70" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="71" spans="10:19">
+      <c r="J71">
+        <v>6</v>
+      </c>
+      <c r="K71">
+        <v>10</v>
+      </c>
+      <c r="L71">
+        <v>17.38</v>
+      </c>
+      <c r="M71">
+        <v>57</v>
+      </c>
+      <c r="N71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="10:19">
+      <c r="J72">
+        <v>6</v>
+      </c>
+      <c r="K72">
+        <v>20</v>
+      </c>
+      <c r="L72">
+        <v>17.079999999999998</v>
+      </c>
+      <c r="M72">
+        <v>48</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/实验记录.xlsx
+++ b/实验记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wuxinghao/Documents/联邦学习/ResearchCode/FedTSP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D776B910-A0FA-5841-87A6-5DA13CB2A55F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF4E6CF-9E4D-6C40-90FD-29CBD52009BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28880" yWindow="-24340" windowWidth="28620" windowHeight="17580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CIFAR100-dir1.0-client20" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="61">
   <si>
     <t>验证文本prompt对训练的影响</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -277,6 +277,10 @@
   </si>
   <si>
     <t>update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>500 rounds</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -623,10 +627,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CCDCA62-1458-6748-AAD6-300D2625CB6F}">
-  <dimension ref="A1:Q118"/>
+  <dimension ref="A1:S118"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -643,7 +647,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
         <v>56</v>
       </c>
@@ -680,11 +684,17 @@
       <c r="M2" t="s">
         <v>10</v>
       </c>
-      <c r="P2" t="s">
+      <c r="N2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>1</v>
       </c>
@@ -721,14 +731,20 @@
       <c r="N3" t="s">
         <v>27</v>
       </c>
-      <c r="P3" t="s">
-        <v>1</v>
+      <c r="O3" t="s">
+        <v>40</v>
       </c>
       <c r="Q3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="S3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4">
         <v>2</v>
       </c>
@@ -765,14 +781,14 @@
       <c r="N4">
         <v>15.99</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>0.1</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>20.25</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:19">
       <c r="A5">
         <v>3</v>
       </c>
@@ -806,11 +822,23 @@
       <c r="M5">
         <v>0.2</v>
       </c>
-      <c r="P5">
+      <c r="N5">
+        <v>17.12</v>
+      </c>
+      <c r="O5">
+        <v>495</v>
+      </c>
+      <c r="Q5">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="R5">
+        <v>20.329999999999998</v>
+      </c>
+      <c r="S5">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>4</v>
       </c>
@@ -844,11 +872,23 @@
       <c r="M6">
         <v>0.3</v>
       </c>
-      <c r="P6">
+      <c r="N6">
+        <v>17.38</v>
+      </c>
+      <c r="O6">
+        <v>237</v>
+      </c>
+      <c r="Q6">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="R6">
+        <v>20.6</v>
+      </c>
+      <c r="S6">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7">
         <v>5</v>
       </c>
@@ -882,11 +922,23 @@
       <c r="M7">
         <v>0.4</v>
       </c>
-      <c r="P7">
+      <c r="N7">
+        <v>17.809999999999999</v>
+      </c>
+      <c r="O7">
+        <v>471</v>
+      </c>
+      <c r="Q7">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7">
+        <v>20.98</v>
+      </c>
+      <c r="S7">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8">
         <v>6</v>
       </c>
@@ -920,11 +972,23 @@
       <c r="M8">
         <v>0.5</v>
       </c>
-      <c r="P8">
+      <c r="N8">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="O8">
+        <v>370</v>
+      </c>
+      <c r="Q8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8">
+        <v>20.89</v>
+      </c>
+      <c r="S8">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9">
         <v>7</v>
       </c>
@@ -956,7 +1020,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:19">
       <c r="A10">
         <v>8</v>
       </c>
@@ -988,7 +1052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:19">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1017,17 +1081,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:19">
       <c r="A12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:19">
       <c r="A13">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:19">
       <c r="A15" t="s">
         <v>57</v>
       </c>
@@ -1062,7 +1126,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:19">
       <c r="A16">
         <v>1</v>
       </c>
@@ -3629,10 +3693,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AFB62DF-B5AA-5E4C-80E6-11565E9C9DBC}">
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:19">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3649,7 +3713,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
         <v>56</v>
       </c>
@@ -3686,11 +3750,17 @@
       <c r="M2" t="s">
         <v>10</v>
       </c>
-      <c r="P2" t="s">
+      <c r="N2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="R2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3727,14 +3797,20 @@
       <c r="N3" t="s">
         <v>27</v>
       </c>
-      <c r="P3" t="s">
-        <v>1</v>
+      <c r="O3" t="s">
+        <v>40</v>
       </c>
       <c r="Q3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="S3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4">
         <v>2</v>
       </c>
@@ -3771,14 +3847,14 @@
       <c r="N4">
         <v>56.39</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>0.1</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>58.37</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:19">
       <c r="A5">
         <v>3</v>
       </c>
@@ -3815,14 +3891,14 @@
       <c r="N5">
         <v>56.94</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>0.2</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>58.81</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:19">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3859,14 +3935,14 @@
       <c r="N6">
         <v>57.27</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>0.3</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>58.84</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:19">
       <c r="A7">
         <v>5</v>
       </c>
@@ -3900,11 +3976,23 @@
       <c r="M7">
         <v>0.4</v>
       </c>
-      <c r="P7">
+      <c r="N7">
+        <v>57.1</v>
+      </c>
+      <c r="O7">
+        <v>422</v>
+      </c>
+      <c r="Q7">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="R7">
+        <v>59.13</v>
+      </c>
+      <c r="S7">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8">
         <v>6</v>
       </c>
@@ -3938,11 +4026,23 @@
       <c r="M8">
         <v>0.5</v>
       </c>
-      <c r="P8">
+      <c r="N8">
+        <v>57.15</v>
+      </c>
+      <c r="O8">
+        <v>423</v>
+      </c>
+      <c r="Q8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="R8">
+        <v>58.89</v>
+      </c>
+      <c r="S8">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9">
         <v>7</v>
       </c>
@@ -3974,7 +4074,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:19">
       <c r="A10">
         <v>8</v>
       </c>
@@ -4006,22 +4106,22 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:19">
       <c r="A11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:19">
       <c r="A12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:19">
       <c r="A13">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:19">
       <c r="A15" t="s">
         <v>57</v>
       </c>
@@ -4056,7 +4156,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:19">
       <c r="A16">
         <v>1</v>
       </c>
